--- a/kuuube's_tablet_buying_guide.xlsx
+++ b/kuuube's_tablet_buying_guide.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Tablet Buying Guide" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Kuuubes Info" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Tablet Buying Guide" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Kuuubes Info" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -17,57 +17,57 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B81">
+    <comment authorId="0" ref="B80">
       <text>
         <t xml:space="preserve">(PTZ-430, PTZ-431W, PTZ-630, PTZ-631W, PTZ-930, PTZ-1230, PTZ-1231W)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B82">
+    <comment authorId="0" ref="B81">
       <text>
         <t xml:space="preserve">(XD-0405-U, XD-0608-U, XD-0912-U, XD-1212-U,  XD-1218-U)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B83">
+    <comment authorId="0" ref="B82">
       <text>
         <t xml:space="preserve">(GD-0405-U, GD-0608-U, GD-0912-U, GD-1212-U, GD-1218-U)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B84">
+    <comment authorId="0" ref="B83">
       <text>
         <t xml:space="preserve">(CTE-460, CTE-660)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B86">
+    <comment authorId="0" ref="B85">
       <text>
         <t xml:space="preserve">(CTE-450, CTE-650)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B87">
+    <comment authorId="0" ref="B86">
       <text>
         <t xml:space="preserve">(CTE-440, CTE-640)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B88">
+    <comment authorId="0" ref="B87">
       <text>
         <t xml:space="preserve">(CTE-430, CTE-630)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B89">
+    <comment authorId="0" ref="B88">
       <text>
         <t xml:space="preserve">(FW-300, FB-630)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B90">
+    <comment authorId="0" ref="B89">
       <text>
         <t xml:space="preserve">(CTF-430, CTF-221, CTF-420)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B91">
+    <comment authorId="0" ref="B90">
       <text>
         <t xml:space="preserve">(FT-0203-U, FT-0405-U)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B92">
+    <comment authorId="0" ref="B91">
       <text>
         <t xml:space="preserve">(ET-0405A-U, ET-0507A-U)</t>
       </text>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="232">
   <si>
     <t>Kuuube's Tablet Buying Guide</t>
   </si>
@@ -562,18 +562,6 @@
     <t>500 USD</t>
   </si>
   <si>
-    <t>Boosted report rate (200hz) compared to consumer line wacom tablets (133hz), extremely high pressure scan rate (pen taps send almost instantly, this is good for tapx), extremely minor anti-chatter on hover, and glitchy position reporting when pen is tilted roughly 15° or lower to the tablet.</t>
-  </si>
-  <si>
-    <t>350 USD</t>
-  </si>
-  <si>
-    <t>PTH-860</t>
-  </si>
-  <si>
-    <t>400-500 USD</t>
-  </si>
-  <si>
     <t>CTC-6110WL</t>
   </si>
   <si>
@@ -620,6 +608,9 @@
   </si>
   <si>
     <t>Secondhand High Budget Options</t>
+  </si>
+  <si>
+    <t>PTH-860</t>
   </si>
   <si>
     <t>PTH-851</t>
@@ -1250,7 +1241,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1362,6 +1353,9 @@
     <xf borderId="0" fillId="0" fontId="25" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1372,6 +1366,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="27" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1430,6 +1427,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2867,37 +2868,39 @@
       <c r="AA29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="37" t="s">
+      <c r="E30" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="H30" s="19" t="s">
+      <c r="H30" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I30" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="J30" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="K30" s="38"/>
+      <c r="I30" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="M30" s="24"/>
       <c r="N30" s="24"/>
       <c r="O30" s="24"/>
@@ -2919,18 +2922,18 @@
         <v>18</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G31" s="23" t="s">
@@ -2943,11 +2946,9 @@
         <v>98</v>
       </c>
       <c r="J31" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="K31" s="21" t="s">
-        <v>102</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K31" s="39"/>
       <c r="M31" s="24"/>
       <c r="N31" s="24"/>
       <c r="O31" s="24"/>
@@ -2969,18 +2970,18 @@
         <v>18</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F32" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G32" s="23" t="s">
@@ -2990,12 +2991,14 @@
         <v>25</v>
       </c>
       <c r="I32" s="20" t="s">
-        <v>26</v>
+        <v>98</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="K32" s="38"/>
+        <v>101</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="M32" s="24"/>
       <c r="N32" s="24"/>
       <c r="O32" s="24"/>
@@ -3017,22 +3020,22 @@
         <v>18</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>21</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="28" t="s">
-        <v>54</v>
+      <c r="G33" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H33" s="19" t="s">
         <v>25</v>
@@ -3040,10 +3043,10 @@
       <c r="I33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="35" t="s">
+      <c r="J33" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="K33" s="38"/>
+      <c r="K33" s="39"/>
       <c r="M33" s="24"/>
       <c r="N33" s="24"/>
       <c r="O33" s="24"/>
@@ -3065,22 +3068,22 @@
         <v>18</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F34" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G34" s="23" t="s">
-        <v>24</v>
+      <c r="G34" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="H34" s="19" t="s">
         <v>25</v>
@@ -3088,12 +3091,10 @@
       <c r="I34" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J34" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="K34" s="21" t="s">
-        <v>109</v>
-      </c>
+      <c r="J34" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" s="39"/>
       <c r="M34" s="24"/>
       <c r="N34" s="24"/>
       <c r="O34" s="24"/>
@@ -3115,10 +3116,10 @@
         <v>18</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>108</v>
@@ -3126,7 +3127,7 @@
       <c r="E35" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G35" s="23" t="s">
@@ -3139,7 +3140,7 @@
         <v>26</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K35" s="21" t="s">
         <v>109</v>
@@ -3165,10 +3166,10 @@
         <v>18</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>108</v>
@@ -3176,11 +3177,11 @@
       <c r="E36" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F36" s="37" t="s">
+      <c r="F36" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G36" s="28" t="s">
-        <v>54</v>
+      <c r="G36" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H36" s="19" t="s">
         <v>25</v>
@@ -3189,7 +3190,7 @@
         <v>26</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K36" s="21" t="s">
         <v>109</v>
@@ -3215,34 +3216,34 @@
         <v>18</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="26" t="s">
-        <v>89</v>
+        <v>111</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>20</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="E37" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F37" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="26" t="s">
-        <v>72</v>
+      <c r="F37" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>25</v>
       </c>
       <c r="I37" s="20" t="s">
         <v>26</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K37" s="21" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M37" s="24"/>
       <c r="N37" s="24"/>
@@ -3265,7 +3266,7 @@
         <v>18</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>89</v>
@@ -3274,13 +3275,13 @@
         <v>76</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F38" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="G38" s="28" t="s">
-        <v>54</v>
+      <c r="G38" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H38" s="26" t="s">
         <v>72</v>
@@ -3288,7 +3289,7 @@
       <c r="I38" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="35" t="s">
+      <c r="J38" s="20" t="s">
         <v>27</v>
       </c>
       <c r="K38" s="21" t="s">
@@ -3311,60 +3312,60 @@
       <c r="AA38" s="24"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H39" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J39" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
+      <c r="S39" s="24"/>
+      <c r="T39" s="24"/>
+      <c r="U39" s="24"/>
+      <c r="V39" s="24"/>
+      <c r="W39" s="24"/>
+      <c r="X39" s="24"/>
+      <c r="Y39" s="24"/>
+      <c r="Z39" s="24"/>
+      <c r="AA39" s="24"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="2"/>
-      <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="2"/>
-      <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
-      <c r="Y39" s="2"/>
-      <c r="Z39" s="2"/>
-      <c r="AA39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>17</v>
-      </c>
+      <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -3382,61 +3383,61 @@
       <c r="AA40" s="2"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I41" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J41" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="K41" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="M41" s="24"/>
-      <c r="N41" s="24"/>
-      <c r="O41" s="24"/>
-      <c r="P41" s="24"/>
-      <c r="Q41" s="24"/>
-      <c r="R41" s="24"/>
-      <c r="S41" s="24"/>
-      <c r="T41" s="24"/>
-      <c r="U41" s="24"/>
-      <c r="V41" s="24"/>
-      <c r="W41" s="24"/>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="24"/>
-      <c r="Z41" s="24"/>
-      <c r="AA41" s="24"/>
+      <c r="A41" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
+      <c r="AA41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" s="18" t="s">
         <v>18</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="C42" s="19" t="s">
         <v>20</v>
@@ -3445,13 +3446,13 @@
         <v>100</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G42" s="28" t="s">
-        <v>54</v>
+      <c r="G42" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H42" s="19" t="s">
         <v>25</v>
@@ -3463,7 +3464,7 @@
         <v>27</v>
       </c>
       <c r="K42" s="21" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="M42" s="24"/>
       <c r="N42" s="24"/>
@@ -3486,34 +3487,34 @@
         <v>18</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" s="26" t="s">
-        <v>70</v>
+        <v>117</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>20</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="F43" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43" s="23" t="s">
-        <v>24</v>
+        <v>118</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="K43" s="21" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="M43" s="24"/>
       <c r="N43" s="24"/>
@@ -3536,34 +3537,34 @@
         <v>18</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F44" s="27" t="s">
-        <v>49</v>
+        <v>121</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>34</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="H44" s="26" t="s">
-        <v>72</v>
+      <c r="H44" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="I44" s="20" t="s">
         <v>98</v>
       </c>
       <c r="J44" s="20" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="K44" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M44" s="24"/>
       <c r="N44" s="24"/>
@@ -3586,22 +3587,22 @@
         <v>18</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C45" s="26" t="s">
         <v>89</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="F45" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="G45" s="28" t="s">
-        <v>54</v>
+      <c r="G45" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H45" s="26" t="s">
         <v>72</v>
@@ -3609,7 +3610,7 @@
       <c r="I45" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="J45" s="35" t="s">
+      <c r="J45" s="20" t="s">
         <v>27</v>
       </c>
       <c r="K45" s="21" t="s">
@@ -3632,60 +3633,60 @@
       <c r="AA45" s="24"/>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F46" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="I46" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="J46" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="K46" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="M46" s="24"/>
+      <c r="N46" s="24"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="24"/>
+      <c r="Q46" s="24"/>
+      <c r="R46" s="24"/>
+      <c r="S46" s="24"/>
+      <c r="T46" s="24"/>
+      <c r="U46" s="24"/>
+      <c r="V46" s="24"/>
+      <c r="W46" s="24"/>
+      <c r="X46" s="24"/>
+      <c r="Y46" s="24"/>
+      <c r="Z46" s="24"/>
+      <c r="AA46" s="24"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="2"/>
-      <c r="T46" s="2"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="2"/>
-      <c r="W46" s="2"/>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K47" s="9" t="s">
-        <v>17</v>
-      </c>
+      <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -3703,61 +3704,61 @@
       <c r="AA47" s="2"/>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="G48" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I48" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="J48" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="K48" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="M48" s="24"/>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="24"/>
-      <c r="R48" s="24"/>
-      <c r="S48" s="24"/>
-      <c r="T48" s="24"/>
-      <c r="U48" s="24"/>
-      <c r="V48" s="24"/>
-      <c r="W48" s="24"/>
-      <c r="X48" s="24"/>
-      <c r="Y48" s="24"/>
-      <c r="Z48" s="24"/>
-      <c r="AA48" s="24"/>
+      <c r="A48" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="2"/>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C49" s="19" t="s">
         <v>31</v>
@@ -3766,13 +3767,13 @@
         <v>108</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="F49" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="G49" s="28" t="s">
-        <v>54</v>
+      <c r="G49" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H49" s="19" t="s">
         <v>25</v>
@@ -3781,7 +3782,7 @@
         <v>130</v>
       </c>
       <c r="J49" s="35" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="K49" s="21" t="s">
         <v>131</v>
@@ -3807,34 +3808,34 @@
         <v>18</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C50" s="19" t="s">
         <v>31</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="F50" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>24</v>
+        <v>133</v>
+      </c>
+      <c r="F50" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="H50" s="19" t="s">
         <v>25</v>
       </c>
       <c r="I50" s="20" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="J50" s="35" t="s">
         <v>101</v>
       </c>
       <c r="K50" s="21" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M50" s="24"/>
       <c r="N50" s="24"/>
@@ -3857,18 +3858,18 @@
         <v>18</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E51" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="F51" s="39" t="s">
+      <c r="F51" s="40" t="s">
         <v>24</v>
       </c>
       <c r="G51" s="23" t="s">
@@ -3884,7 +3885,7 @@
         <v>101</v>
       </c>
       <c r="K51" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M51" s="24"/>
       <c r="N51" s="24"/>
@@ -3907,18 +3908,18 @@
         <v>18</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="F52" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="F52" s="40" t="s">
         <v>24</v>
       </c>
       <c r="G52" s="23" t="s">
@@ -3934,7 +3935,7 @@
         <v>101</v>
       </c>
       <c r="K52" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="M52" s="24"/>
       <c r="N52" s="24"/>
@@ -3957,22 +3958,22 @@
         <v>18</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>31</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="F53" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="F53" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G53" s="28" t="s">
-        <v>54</v>
+      <c r="G53" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H53" s="19" t="s">
         <v>25</v>
@@ -3984,7 +3985,7 @@
         <v>101</v>
       </c>
       <c r="K53" s="21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M53" s="24"/>
       <c r="N53" s="24"/>
@@ -4007,18 +4008,18 @@
         <v>18</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="F54" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" s="40" t="s">
         <v>24</v>
       </c>
       <c r="G54" s="28" t="s">
@@ -4034,7 +4035,7 @@
         <v>101</v>
       </c>
       <c r="K54" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M54" s="24"/>
       <c r="N54" s="24"/>
@@ -4057,18 +4058,18 @@
         <v>18</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F55" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="F55" s="40" t="s">
         <v>24</v>
       </c>
       <c r="G55" s="28" t="s">
@@ -4107,22 +4108,22 @@
         <v>18</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E56" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="F56" s="39" t="s">
+      <c r="F56" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G56" s="40" t="s">
-        <v>147</v>
+      <c r="G56" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="H56" s="19" t="s">
         <v>25</v>
@@ -4157,7 +4158,7 @@
         <v>18</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>20</v>
@@ -4166,13 +4167,13 @@
         <v>21</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="28" t="s">
-        <v>54</v>
+        <v>128</v>
+      </c>
+      <c r="F57" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="41" t="s">
+        <v>147</v>
       </c>
       <c r="H57" s="19" t="s">
         <v>25</v>
@@ -4181,9 +4182,11 @@
         <v>98</v>
       </c>
       <c r="J57" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="K57" s="38"/>
+        <v>101</v>
+      </c>
+      <c r="K57" s="21" t="s">
+        <v>137</v>
+      </c>
       <c r="M57" s="24"/>
       <c r="N57" s="24"/>
       <c r="O57" s="24"/>
@@ -4201,22 +4204,22 @@
       <c r="AA57" s="24"/>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>150</v>
+      <c r="B58" s="42" t="s">
+        <v>117</v>
       </c>
       <c r="C58" s="19" t="s">
         <v>31</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="F58" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G58" s="28" t="s">
@@ -4226,13 +4229,13 @@
         <v>25</v>
       </c>
       <c r="I58" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="J58" s="35" t="s">
-        <v>101</v>
+        <v>26</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>27</v>
       </c>
       <c r="K58" s="21" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="M58" s="24"/>
       <c r="N58" s="24"/>
@@ -4251,182 +4254,180 @@
       <c r="AA58" s="24"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="J59" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="K59" s="39"/>
+      <c r="M59" s="24"/>
+      <c r="N59" s="24"/>
+      <c r="O59" s="24"/>
+      <c r="P59" s="24"/>
+      <c r="Q59" s="24"/>
+      <c r="R59" s="24"/>
+      <c r="S59" s="24"/>
+      <c r="T59" s="24"/>
+      <c r="U59" s="24"/>
+      <c r="V59" s="24"/>
+      <c r="W59" s="24"/>
+      <c r="X59" s="24"/>
+      <c r="Y59" s="24"/>
+      <c r="Z59" s="24"/>
+      <c r="AA59" s="24"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F60" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="H60" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="J60" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="K60" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="M60" s="24"/>
+      <c r="N60" s="24"/>
+      <c r="O60" s="24"/>
+      <c r="P60" s="24"/>
+      <c r="Q60" s="24"/>
+      <c r="R60" s="24"/>
+      <c r="S60" s="24"/>
+      <c r="T60" s="24"/>
+      <c r="U60" s="24"/>
+      <c r="V60" s="24"/>
+      <c r="W60" s="24"/>
+      <c r="X60" s="24"/>
+      <c r="Y60" s="24"/>
+      <c r="Z60" s="24"/>
+      <c r="AA60" s="24"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-      <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2"/>
-      <c r="W59" s="2"/>
-      <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="2"/>
-      <c r="AA59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="s">
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2"/>
+      <c r="W61" s="2"/>
+      <c r="X61" s="2"/>
+      <c r="Y61" s="2"/>
+      <c r="Z61" s="2"/>
+      <c r="AA61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B62" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C62" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D62" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E62" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="10" t="s">
+      <c r="F62" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G62" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="H62" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I62" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J60" s="9" t="s">
+      <c r="J62" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K60" s="9" t="s">
+      <c r="K62" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
-      <c r="T60" s="2"/>
-      <c r="U60" s="2"/>
-      <c r="V60" s="2"/>
-      <c r="W60" s="2"/>
-      <c r="X60" s="2"/>
-      <c r="Y60" s="2"/>
-      <c r="Z60" s="2"/>
-      <c r="AA60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C61" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="F61" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="G61" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H61" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I61" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="J61" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="K61" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
-      <c r="R61" s="24"/>
-      <c r="S61" s="24"/>
-      <c r="T61" s="24"/>
-      <c r="U61" s="24"/>
-      <c r="V61" s="24"/>
-      <c r="W61" s="24"/>
-      <c r="X61" s="24"/>
-      <c r="Y61" s="24"/>
-      <c r="Z61" s="24"/>
-      <c r="AA61" s="24"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="C62" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="F62" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="G62" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I62" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="J62" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="K62" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="M62" s="24"/>
-      <c r="N62" s="24"/>
-      <c r="O62" s="24"/>
-      <c r="P62" s="24"/>
-      <c r="Q62" s="24"/>
-      <c r="R62" s="24"/>
-      <c r="S62" s="24"/>
-      <c r="T62" s="24"/>
-      <c r="U62" s="24"/>
-      <c r="V62" s="24"/>
-      <c r="W62" s="24"/>
-      <c r="X62" s="24"/>
-      <c r="Y62" s="24"/>
-      <c r="Z62" s="24"/>
-      <c r="AA62" s="24"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
+      <c r="Y62" s="2"/>
+      <c r="Z62" s="2"/>
+      <c r="AA62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="18" t="s">
         <v>18</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C63" s="29" t="s">
         <v>153</v>
@@ -4435,13 +4436,13 @@
         <v>154</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="F63" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F63" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="G63" s="40" t="s">
-        <v>147</v>
+      <c r="G63" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H63" s="19" t="s">
         <v>25</v>
@@ -4476,34 +4477,34 @@
         <v>18</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C64" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="D64" s="20" t="s">
-        <v>47</v>
+      <c r="D64" s="21" t="s">
+        <v>154</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="F64" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="F64" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="G64" s="23" t="s">
-        <v>24</v>
+      <c r="G64" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="H64" s="19" t="s">
         <v>25</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="J64" s="35" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="K64" s="21" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M64" s="24"/>
       <c r="N64" s="24"/>
@@ -4526,34 +4527,34 @@
         <v>18</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C65" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="D65" s="20" t="s">
-        <v>47</v>
+      <c r="D65" s="21" t="s">
+        <v>154</v>
       </c>
       <c r="E65" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="F65" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F65" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="G65" s="28" t="s">
-        <v>54</v>
+      <c r="G65" s="41" t="s">
+        <v>147</v>
       </c>
       <c r="H65" s="19" t="s">
         <v>25</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="J65" s="35" t="s">
         <v>101</v>
       </c>
       <c r="K65" s="21" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M65" s="24"/>
       <c r="N65" s="24"/>
@@ -4576,34 +4577,34 @@
         <v>18</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C66" s="29" t="s">
-        <v>153</v>
+        <v>161</v>
+      </c>
+      <c r="C66" s="26" t="s">
+        <v>70</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="F66" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="G66" s="40" t="s">
-        <v>147</v>
+        <v>162</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I66" s="20" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="J66" s="35" t="s">
         <v>101</v>
       </c>
       <c r="K66" s="21" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="M66" s="24"/>
       <c r="N66" s="24"/>
@@ -4622,38 +4623,38 @@
       <c r="AA66" s="24"/>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B67" s="18" t="s">
-        <v>165</v>
+      <c r="A67" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>163</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="F67" s="22" t="s">
-        <v>34</v>
+        <v>164</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>82</v>
       </c>
       <c r="G67" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="H67" s="19" t="s">
-        <v>35</v>
+      <c r="H67" s="26" t="s">
+        <v>72</v>
       </c>
       <c r="I67" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="J67" s="35" t="s">
-        <v>101</v>
+      <c r="J67" s="20" t="s">
+        <v>37</v>
       </c>
       <c r="K67" s="21" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="M67" s="24"/>
       <c r="N67" s="24"/>
@@ -4672,11 +4673,11 @@
       <c r="AA67" s="24"/>
     </row>
     <row r="68">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B68" s="21" t="s">
-        <v>167</v>
+      <c r="B68" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="C68" s="26" t="s">
         <v>89</v>
@@ -4685,13 +4686,13 @@
         <v>80</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F68" s="33" t="s">
         <v>82</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="H68" s="26" t="s">
         <v>72</v>
@@ -4703,7 +4704,7 @@
         <v>37</v>
       </c>
       <c r="K68" s="21" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M68" s="24"/>
       <c r="N68" s="24"/>
@@ -4722,11 +4723,11 @@
       <c r="AA68" s="24"/>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="s">
+      <c r="A69" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B69" s="18" t="s">
-        <v>170</v>
+      <c r="B69" s="21" t="s">
+        <v>169</v>
       </c>
       <c r="C69" s="26" t="s">
         <v>89</v>
@@ -4735,13 +4736,13 @@
         <v>80</v>
       </c>
       <c r="E69" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F69" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="G69" s="28" t="s">
-        <v>172</v>
+      <c r="G69" s="41" t="s">
+        <v>171</v>
       </c>
       <c r="H69" s="26" t="s">
         <v>72</v>
@@ -4753,7 +4754,7 @@
         <v>37</v>
       </c>
       <c r="K69" s="21" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M69" s="24"/>
       <c r="N69" s="24"/>
@@ -4772,10 +4773,10 @@
       <c r="AA69" s="24"/>
     </row>
     <row r="70">
-      <c r="A70" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="21" t="s">
+      <c r="A70" s="43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B70" s="43" t="s">
         <v>173</v>
       </c>
       <c r="C70" s="26" t="s">
@@ -4787,74 +4788,45 @@
       <c r="E70" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="F70" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="G70" s="40" t="s">
-        <v>175</v>
+      <c r="F70" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="H70" s="26" t="s">
         <v>72</v>
       </c>
       <c r="I70" s="20" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="J70" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="K70" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="M70" s="24"/>
-      <c r="N70" s="24"/>
-      <c r="O70" s="24"/>
-      <c r="P70" s="24"/>
-      <c r="Q70" s="24"/>
-      <c r="R70" s="24"/>
-      <c r="S70" s="24"/>
-      <c r="T70" s="24"/>
-      <c r="U70" s="24"/>
-      <c r="V70" s="24"/>
-      <c r="W70" s="24"/>
-      <c r="X70" s="24"/>
-      <c r="Y70" s="24"/>
-      <c r="Z70" s="24"/>
-      <c r="AA70" s="24"/>
+      <c r="K70" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
+      <c r="Y70" s="2"/>
+      <c r="Z70" s="2"/>
+      <c r="AA70" s="2"/>
     </row>
     <row r="71">
-      <c r="A71" s="41" t="s">
+      <c r="A71" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B71" s="41" t="s">
-        <v>177</v>
-      </c>
-      <c r="C71" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="D71" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E71" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="F71" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="G71" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H71" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="I71" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J71" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="K71" s="42" t="s">
-        <v>179</v>
-      </c>
+      <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -4872,10 +4844,39 @@
       <c r="AA71" s="2"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="L72" s="2"/>
+      <c r="A72" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -4893,61 +4894,61 @@
       <c r="AA72" s="2"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K73" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
-      <c r="T73" s="2"/>
-      <c r="U73" s="2"/>
-      <c r="V73" s="2"/>
-      <c r="W73" s="2"/>
-      <c r="X73" s="2"/>
-      <c r="Y73" s="2"/>
-      <c r="Z73" s="2"/>
-      <c r="AA73" s="2"/>
+      <c r="A73" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="G73" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="H73" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="J73" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="K73" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="M73" s="24"/>
+      <c r="N73" s="24"/>
+      <c r="O73" s="24"/>
+      <c r="P73" s="24"/>
+      <c r="Q73" s="24"/>
+      <c r="R73" s="24"/>
+      <c r="S73" s="24"/>
+      <c r="T73" s="24"/>
+      <c r="U73" s="24"/>
+      <c r="V73" s="24"/>
+      <c r="W73" s="24"/>
+      <c r="X73" s="24"/>
+      <c r="Y73" s="24"/>
+      <c r="Z73" s="24"/>
+      <c r="AA73" s="24"/>
     </row>
     <row r="74">
       <c r="A74" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C74" s="19" t="s">
         <v>31</v>
@@ -4956,25 +4957,25 @@
         <v>108</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="F74" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="G74" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="F74" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G74" s="41" t="s">
         <v>147</v>
       </c>
       <c r="H74" s="19" t="s">
         <v>25</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="J74" s="35" t="s">
         <v>101</v>
       </c>
       <c r="K74" s="21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="M74" s="24"/>
       <c r="N74" s="24"/>
@@ -4997,7 +4998,7 @@
         <v>18</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C75" s="19" t="s">
         <v>31</v>
@@ -5006,12 +5007,12 @@
         <v>108</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="F75" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="F75" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G75" s="40" t="s">
+      <c r="G75" s="41" t="s">
         <v>147</v>
       </c>
       <c r="H75" s="19" t="s">
@@ -5024,7 +5025,7 @@
         <v>101</v>
       </c>
       <c r="K75" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M75" s="24"/>
       <c r="N75" s="24"/>
@@ -5043,58 +5044,29 @@
       <c r="AA75" s="24"/>
     </row>
     <row r="76">
-      <c r="A76" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B76" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D76" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E76" s="21" t="s">
+      <c r="A76" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="2"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="2"/>
+      <c r="W76" s="2"/>
+      <c r="X76" s="2"/>
+      <c r="Y76" s="2"/>
+      <c r="Z76" s="2"/>
+      <c r="AA76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="45" t="s">
         <v>182</v>
-      </c>
-      <c r="F76" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="G76" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="H76" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I76" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="J76" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="K76" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="M76" s="24"/>
-      <c r="N76" s="24"/>
-      <c r="O76" s="24"/>
-      <c r="P76" s="24"/>
-      <c r="Q76" s="24"/>
-      <c r="R76" s="24"/>
-      <c r="S76" s="24"/>
-      <c r="T76" s="24"/>
-      <c r="U76" s="24"/>
-      <c r="V76" s="24"/>
-      <c r="W76" s="24"/>
-      <c r="X76" s="24"/>
-      <c r="Y76" s="24"/>
-      <c r="Z76" s="24"/>
-      <c r="AA76" s="24"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="s">
-        <v>184</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -5114,97 +5086,126 @@
       <c r="AA77" s="2"/>
     </row>
     <row r="78">
-      <c r="A78" s="43" t="s">
+      <c r="A78" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M78" s="46"/>
+      <c r="N78" s="46"/>
+      <c r="O78" s="46"/>
+      <c r="P78" s="46"/>
+      <c r="Q78" s="46"/>
+      <c r="R78" s="46"/>
+      <c r="S78" s="46"/>
+      <c r="T78" s="46"/>
+      <c r="U78" s="46"/>
+      <c r="V78" s="46"/>
+      <c r="W78" s="46"/>
+      <c r="X78" s="46"/>
+      <c r="Y78" s="46"/>
+      <c r="Z78" s="46"/>
+      <c r="AA78" s="46"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D79" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
-      <c r="Y78" s="2"/>
-      <c r="Z78" s="2"/>
-      <c r="AA78" s="2"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I79" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J79" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M79" s="44"/>
-      <c r="N79" s="44"/>
-      <c r="O79" s="44"/>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
-      <c r="R79" s="44"/>
-      <c r="S79" s="44"/>
-      <c r="T79" s="44"/>
-      <c r="U79" s="44"/>
-      <c r="V79" s="44"/>
-      <c r="W79" s="44"/>
-      <c r="X79" s="44"/>
-      <c r="Y79" s="44"/>
-      <c r="Z79" s="44"/>
-      <c r="AA79" s="44"/>
+      <c r="E79" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F79" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="G79" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="H79" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="J79" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="K79" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="M79" s="24"/>
+      <c r="N79" s="24"/>
+      <c r="O79" s="24"/>
+      <c r="P79" s="24"/>
+      <c r="Q79" s="24"/>
+      <c r="R79" s="24"/>
+      <c r="S79" s="24"/>
+      <c r="T79" s="24"/>
+      <c r="U79" s="24"/>
+      <c r="V79" s="24"/>
+      <c r="W79" s="24"/>
+      <c r="X79" s="24"/>
+      <c r="Y79" s="24"/>
+      <c r="Z79" s="24"/>
+      <c r="AA79" s="24"/>
     </row>
     <row r="80">
       <c r="A80" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B80" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E80" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="C80" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E80" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F80" s="39" t="s">
+      <c r="F80" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G80" s="45" t="s">
-        <v>190</v>
+      <c r="G80" s="21" t="s">
+        <v>191</v>
       </c>
       <c r="H80" s="19" t="s">
         <v>25</v>
@@ -5213,10 +5214,10 @@
         <v>98</v>
       </c>
       <c r="J80" s="35" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="K80" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M80" s="24"/>
       <c r="N80" s="24"/>
@@ -5242,19 +5243,19 @@
         <v>192</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E81" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F81" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F81" s="40" t="s">
         <v>24</v>
       </c>
       <c r="G81" s="21" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H81" s="19" t="s">
         <v>25</v>
@@ -5263,10 +5264,10 @@
         <v>98</v>
       </c>
       <c r="J81" s="35" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="K81" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M81" s="24"/>
       <c r="N81" s="24"/>
@@ -5289,22 +5290,22 @@
         <v>18</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F82" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F82" s="40" t="s">
         <v>24</v>
       </c>
       <c r="G82" s="21" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H82" s="19" t="s">
         <v>25</v>
@@ -5313,10 +5314,10 @@
         <v>98</v>
       </c>
       <c r="J82" s="35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K82" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M82" s="24"/>
       <c r="N82" s="24"/>
@@ -5339,34 +5340,34 @@
         <v>18</v>
       </c>
       <c r="B83" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E83" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F83" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83" s="23" t="s">
         <v>197</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E83" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F83" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="G83" s="21" t="s">
-        <v>194</v>
       </c>
       <c r="H83" s="19" t="s">
         <v>25</v>
       </c>
       <c r="I83" s="20" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="J83" s="35" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K83" s="21" t="s">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="M83" s="24"/>
       <c r="N83" s="24"/>
@@ -5389,35 +5390,33 @@
         <v>18</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F84" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F84" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G84" s="23" t="s">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="H84" s="19" t="s">
         <v>25</v>
       </c>
       <c r="I84" s="20" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J84" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="K84" s="21" t="s">
-        <v>109</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="K84" s="39"/>
       <c r="M84" s="24"/>
       <c r="N84" s="24"/>
       <c r="O84" s="24"/>
@@ -5439,33 +5438,33 @@
         <v>18</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E85" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F85" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F85" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G85" s="23" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="H85" s="19" t="s">
         <v>25</v>
       </c>
       <c r="I85" s="20" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J85" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="K85" s="38"/>
+        <v>198</v>
+      </c>
+      <c r="K85" s="39"/>
       <c r="M85" s="24"/>
       <c r="N85" s="24"/>
       <c r="O85" s="24"/>
@@ -5487,22 +5486,22 @@
         <v>18</v>
       </c>
       <c r="B86" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F86" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" s="23" t="s">
         <v>203</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D86" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E86" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G86" s="23" t="s">
-        <v>204</v>
       </c>
       <c r="H86" s="19" t="s">
         <v>25</v>
@@ -5511,9 +5510,11 @@
         <v>36</v>
       </c>
       <c r="J86" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="K86" s="38"/>
+        <v>198</v>
+      </c>
+      <c r="K86" s="21" t="s">
+        <v>204</v>
+      </c>
       <c r="M86" s="24"/>
       <c r="N86" s="24"/>
       <c r="O86" s="24"/>
@@ -5538,15 +5539,15 @@
         <v>205</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E87" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F87" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G87" s="23" t="s">
@@ -5559,10 +5560,10 @@
         <v>36</v>
       </c>
       <c r="J87" s="35" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="K87" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M87" s="24"/>
       <c r="N87" s="24"/>
@@ -5585,22 +5586,22 @@
         <v>18</v>
       </c>
       <c r="B88" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E88" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F88" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G88" s="26" t="s">
         <v>208</v>
-      </c>
-      <c r="C88" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D88" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E88" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F88" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G88" s="23" t="s">
-        <v>209</v>
       </c>
       <c r="H88" s="19" t="s">
         <v>25</v>
@@ -5609,10 +5610,10 @@
         <v>36</v>
       </c>
       <c r="J88" s="35" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K88" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M88" s="24"/>
       <c r="N88" s="24"/>
@@ -5635,22 +5636,22 @@
         <v>18</v>
       </c>
       <c r="B89" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E89" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F89" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G89" s="26" t="s">
         <v>210</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D89" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E89" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F89" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G89" s="26" t="s">
-        <v>211</v>
       </c>
       <c r="H89" s="19" t="s">
         <v>25</v>
@@ -5659,10 +5660,10 @@
         <v>36</v>
       </c>
       <c r="J89" s="35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K89" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M89" s="24"/>
       <c r="N89" s="24"/>
@@ -5685,22 +5686,22 @@
         <v>18</v>
       </c>
       <c r="B90" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F90" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="26" t="s">
         <v>212</v>
-      </c>
-      <c r="C90" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D90" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E90" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F90" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G90" s="26" t="s">
-        <v>213</v>
       </c>
       <c r="H90" s="19" t="s">
         <v>25</v>
@@ -5709,10 +5710,10 @@
         <v>36</v>
       </c>
       <c r="J90" s="35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K90" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M90" s="24"/>
       <c r="N90" s="24"/>
@@ -5735,22 +5736,22 @@
         <v>18</v>
       </c>
       <c r="B91" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F91" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G91" s="23" t="s">
         <v>214</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D91" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E91" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F91" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G91" s="26" t="s">
-        <v>215</v>
       </c>
       <c r="H91" s="19" t="s">
         <v>25</v>
@@ -5759,10 +5760,10 @@
         <v>36</v>
       </c>
       <c r="J91" s="35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K91" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M91" s="24"/>
       <c r="N91" s="24"/>
@@ -5785,22 +5786,22 @@
         <v>18</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E92" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F92" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F92" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G92" s="23" t="s">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="H92" s="19" t="s">
         <v>25</v>
@@ -5809,10 +5810,10 @@
         <v>36</v>
       </c>
       <c r="J92" s="35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K92" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M92" s="24"/>
       <c r="N92" s="24"/>
@@ -5835,18 +5836,18 @@
         <v>18</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E93" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F93" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F93" s="38" t="s">
         <v>23</v>
       </c>
       <c r="G93" s="23" t="s">
@@ -5859,10 +5860,10 @@
         <v>36</v>
       </c>
       <c r="J93" s="35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="K93" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M93" s="24"/>
       <c r="N93" s="24"/>
@@ -5881,39 +5882,18 @@
       <c r="AA93" s="24"/>
     </row>
     <row r="94">
-      <c r="A94" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B94" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="C94" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D94" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F94" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="G94" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H94" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I94" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="J94" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="K94" s="21" t="s">
-        <v>207</v>
-      </c>
+      <c r="A94" s="24"/>
+      <c r="B94" s="24"/>
+      <c r="C94" s="24"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="24"/>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="24"/>
+      <c r="J94" s="24"/>
+      <c r="K94" s="24"/>
+      <c r="L94" s="24"/>
       <c r="M94" s="24"/>
       <c r="N94" s="24"/>
       <c r="O94" s="24"/>
@@ -32726,38 +32706,8 @@
       <c r="Z1018" s="24"/>
       <c r="AA1018" s="24"/>
     </row>
-    <row r="1019">
-      <c r="A1019" s="24"/>
-      <c r="B1019" s="24"/>
-      <c r="C1019" s="24"/>
-      <c r="D1019" s="24"/>
-      <c r="E1019" s="24"/>
-      <c r="F1019" s="24"/>
-      <c r="G1019" s="24"/>
-      <c r="H1019" s="24"/>
-      <c r="I1019" s="24"/>
-      <c r="J1019" s="24"/>
-      <c r="K1019" s="24"/>
-      <c r="L1019" s="24"/>
-      <c r="M1019" s="24"/>
-      <c r="N1019" s="24"/>
-      <c r="O1019" s="24"/>
-      <c r="P1019" s="24"/>
-      <c r="Q1019" s="24"/>
-      <c r="R1019" s="24"/>
-      <c r="S1019" s="24"/>
-      <c r="T1019" s="24"/>
-      <c r="U1019" s="24"/>
-      <c r="V1019" s="24"/>
-      <c r="W1019" s="24"/>
-      <c r="X1019" s="24"/>
-      <c r="Y1019" s="24"/>
-      <c r="Z1019" s="24"/>
-      <c r="AA1019" s="24"/>
-    </row>
   </sheetData>
-  <mergeCells count="94">
-    <mergeCell ref="K47:L47"/>
+  <mergeCells count="93">
     <mergeCell ref="K48:L48"/>
     <mergeCell ref="K49:L49"/>
     <mergeCell ref="K50:L50"/>
@@ -32768,28 +32718,28 @@
     <mergeCell ref="K55:L55"/>
     <mergeCell ref="K56:L56"/>
     <mergeCell ref="K57:L57"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="K62:L62"/>
     <mergeCell ref="K58:L58"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="K67:L67"/>
     <mergeCell ref="K68:L68"/>
     <mergeCell ref="K69:L69"/>
     <mergeCell ref="K70:L70"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="A72:K72"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="A71:K71"/>
     <mergeCell ref="K63:L63"/>
     <mergeCell ref="K64:L64"/>
     <mergeCell ref="K65:L65"/>
     <mergeCell ref="K66:L66"/>
-    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="K72:L72"/>
     <mergeCell ref="K73:L73"/>
     <mergeCell ref="K74:L74"/>
     <mergeCell ref="K75:L75"/>
-    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="A76:K76"/>
     <mergeCell ref="A77:K77"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="K86:L86"/>
     <mergeCell ref="K87:L87"/>
     <mergeCell ref="K88:L88"/>
     <mergeCell ref="K89:L89"/>
@@ -32797,14 +32747,13 @@
     <mergeCell ref="K91:L91"/>
     <mergeCell ref="K92:L92"/>
     <mergeCell ref="K93:L93"/>
-    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="K79:L79"/>
     <mergeCell ref="K80:L80"/>
     <mergeCell ref="K81:L81"/>
     <mergeCell ref="K82:L82"/>
     <mergeCell ref="K83:L83"/>
     <mergeCell ref="K84:L84"/>
     <mergeCell ref="K85:L85"/>
-    <mergeCell ref="K86:L86"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -32833,24 +32782,25 @@
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="K36:L36"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="K38:L38"/>
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K30:L30"/>
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="K34:L34"/>
     <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K30:L30"/>
     <mergeCell ref="K41:L41"/>
     <mergeCell ref="K42:L42"/>
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="K44:L44"/>
     <mergeCell ref="K45:L45"/>
-    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A47:K47"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId2" ref="A9"/>
@@ -32889,41 +32839,35 @@
     <hyperlink r:id="rId35" ref="B26"/>
     <hyperlink r:id="rId36" ref="A27"/>
     <hyperlink r:id="rId37" ref="B27"/>
-    <hyperlink r:id="rId38" ref="A41"/>
-    <hyperlink r:id="rId39" ref="B41"/>
-    <hyperlink r:id="rId40" ref="A42"/>
-    <hyperlink r:id="rId41" ref="B42"/>
-    <hyperlink r:id="rId42" ref="A43"/>
-    <hyperlink r:id="rId43" ref="B43"/>
-    <hyperlink r:id="rId44" ref="A44"/>
-    <hyperlink r:id="rId45" ref="B44"/>
-    <hyperlink r:id="rId46" ref="A45"/>
-    <hyperlink r:id="rId47" ref="B45"/>
-    <hyperlink r:id="rId48" ref="A61"/>
-    <hyperlink r:id="rId49" ref="B61"/>
-    <hyperlink r:id="rId50" ref="A62"/>
-    <hyperlink r:id="rId51" ref="B62"/>
-    <hyperlink r:id="rId52" ref="A63"/>
-    <hyperlink r:id="rId53" ref="B63"/>
-    <hyperlink r:id="rId54" ref="A64"/>
-    <hyperlink r:id="rId55" ref="B64"/>
-    <hyperlink r:id="rId56" ref="A65"/>
-    <hyperlink r:id="rId57" ref="B65"/>
-    <hyperlink r:id="rId58" ref="A66"/>
-    <hyperlink r:id="rId59" ref="B66"/>
-    <hyperlink r:id="rId60" ref="A67"/>
-    <hyperlink r:id="rId61" ref="B67"/>
-    <hyperlink r:id="rId62" ref="A69"/>
-    <hyperlink r:id="rId63" ref="B69"/>
-    <hyperlink r:id="rId64" ref="A71"/>
-    <hyperlink r:id="rId65" ref="B71"/>
-    <hyperlink r:id="rId66" ref="A78"/>
+    <hyperlink r:id="rId38" ref="A42"/>
+    <hyperlink r:id="rId39" ref="B42"/>
+    <hyperlink r:id="rId40" ref="A43"/>
+    <hyperlink r:id="rId41" ref="B43"/>
+    <hyperlink r:id="rId42" ref="A44"/>
+    <hyperlink r:id="rId43" ref="B44"/>
+    <hyperlink r:id="rId44" ref="A45"/>
+    <hyperlink r:id="rId45" ref="B45"/>
+    <hyperlink r:id="rId46" ref="A46"/>
+    <hyperlink r:id="rId47" ref="B46"/>
+    <hyperlink r:id="rId48" ref="A63"/>
+    <hyperlink r:id="rId49" ref="B63"/>
+    <hyperlink r:id="rId50" ref="A64"/>
+    <hyperlink r:id="rId51" ref="B64"/>
+    <hyperlink r:id="rId52" ref="A65"/>
+    <hyperlink r:id="rId53" ref="B65"/>
+    <hyperlink r:id="rId54" ref="A66"/>
+    <hyperlink r:id="rId55" ref="B66"/>
+    <hyperlink r:id="rId56" ref="A68"/>
+    <hyperlink r:id="rId57" ref="B68"/>
+    <hyperlink r:id="rId58" ref="A70"/>
+    <hyperlink r:id="rId59" ref="B70"/>
+    <hyperlink r:id="rId60" ref="A77"/>
   </hyperlinks>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId67"/>
-  <legacyDrawing r:id="rId68"/>
+  <drawing r:id="rId61"/>
+  <legacyDrawing r:id="rId62"/>
 </worksheet>
 </file>
 
@@ -32935,91 +32879,91 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="50" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="47" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="47" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="48" t="s">
-        <v>223</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="51" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="str">
+      <c r="A6" s="51" t="str">
         <f>HYPERLINK("https://docs.google.com/spreadsheets/d/125LNzGmidy1gagwYUt12tRhrNdrWFHhWon7kxWY7iWU","Kuuube's Wacom Tablet Mastersheet")</f>
         <v>Kuuube's Wacom Tablet Mastersheet</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="51" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="52" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="50" t="s">
+    <row r="11">
+      <c r="A11" s="54" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="51" t="s">
+    <row r="12">
+      <c r="A12" s="51" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="48" t="s">
+    <row r="13">
+      <c r="A13" s="51" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="52" t="s">
+    <row r="14">
+      <c r="A14" s="51" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="49" t="s">
+    <row r="15">
+      <c r="A15" s="51" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="49" t="s">
+    <row r="16">
+      <c r="A16" s="55" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="49" t="s">
+    <row r="17">
+      <c r="A17" s="53" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="49" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="53" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="K17" s="54"/>
+      <c r="K17" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/kuuube's_tablet_buying_guide.xlsx
+++ b/kuuube's_tablet_buying_guide.xlsx
@@ -1241,7 +1241,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1409,9 +1409,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="37" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -32718,20 +32715,20 @@
     <mergeCell ref="K55:L55"/>
     <mergeCell ref="K56:L56"/>
     <mergeCell ref="K57:L57"/>
+    <mergeCell ref="K58:L58"/>
     <mergeCell ref="K59:L59"/>
     <mergeCell ref="K60:L60"/>
     <mergeCell ref="A61:K61"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="K68:L68"/>
     <mergeCell ref="K69:L69"/>
     <mergeCell ref="K70:L70"/>
     <mergeCell ref="A71:K71"/>
+    <mergeCell ref="K62:L62"/>
     <mergeCell ref="K63:L63"/>
     <mergeCell ref="K64:L64"/>
     <mergeCell ref="K65:L65"/>
     <mergeCell ref="K66:L66"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="K68:L68"/>
     <mergeCell ref="K72:L72"/>
     <mergeCell ref="K73:L73"/>
     <mergeCell ref="K74:L74"/>
@@ -32782,18 +32779,18 @@
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="A28:K28"/>
+    <mergeCell ref="K36:L36"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="K38:L38"/>
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="A40:K40"/>
     <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="K34:L34"/>
     <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="K30:L30"/>
     <mergeCell ref="K41:L41"/>
     <mergeCell ref="K42:L42"/>
     <mergeCell ref="K43:L43"/>
@@ -32963,7 +32960,6 @@
       <c r="A17" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="K17" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -32976,7 +32972,7 @@
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A17:K17"/>
     <mergeCell ref="A8:K8"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A10:K10"/>
